--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49362,6 +49362,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2131">
+      <c r="A2131" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2131" t="n">
+        <v>3750</v>
+      </c>
+      <c r="C2131" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D2131" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="E2131" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="F2131" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="G2131" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49385,6 +49385,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2132">
+      <c r="A2132" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2132" t="n">
+        <v>6875</v>
+      </c>
+      <c r="C2132" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2132" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E2132" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F2132" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2132" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49408,6 +49408,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2133">
+      <c r="A2133" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2133" t="n">
+        <v>1875</v>
+      </c>
+      <c r="C2133" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D2133" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E2133" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F2133" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="G2133" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49431,6 +49431,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2134">
+      <c r="A2134" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2134" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C2134" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D2134" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2134" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2134" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2134" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49272,7 +49272,7 @@
     </row>
     <row r="2127">
       <c r="A2127" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2127" t="n">
         <v>0</v>
@@ -49295,10 +49295,10 @@
     </row>
     <row r="2128">
       <c r="A2128" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2128" t="n">
-        <v>1875</v>
+        <v>0</v>
       </c>
       <c r="C2128" t="n">
         <v>2.38000011444092</v>
@@ -49318,10 +49318,10 @@
     </row>
     <row r="2129">
       <c r="A2129" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2129" t="n">
-        <v>3750</v>
+        <v>1875</v>
       </c>
       <c r="C2129" t="n">
         <v>2.38000011444092</v>
@@ -49341,10 +49341,10 @@
     </row>
     <row r="2130">
       <c r="A2130" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2130" t="n">
-        <v>625</v>
+        <v>3750</v>
       </c>
       <c r="C2130" t="n">
         <v>2.38000011444092</v>
@@ -49364,19 +49364,19 @@
     </row>
     <row r="2131">
       <c r="A2131" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2131" t="n">
-        <v>3750</v>
+        <v>625</v>
       </c>
       <c r="C2131" t="n">
         <v>2.38000011444092</v>
       </c>
       <c r="D2131" t="n">
-        <v>2.35999989509583</v>
+        <v>2.38000011444092</v>
       </c>
       <c r="E2131" t="n">
-        <v>2.35999989509583</v>
+        <v>2.38000011444092</v>
       </c>
       <c r="F2131" t="n">
         <v>2.38000011444092</v>
@@ -49387,22 +49387,22 @@
     </row>
     <row r="2132">
       <c r="A2132" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2132" t="n">
-        <v>6875</v>
+        <v>3750</v>
       </c>
       <c r="C2132" t="n">
-        <v>2.40000009536743</v>
+        <v>2.38000011444092</v>
       </c>
       <c r="D2132" t="n">
-        <v>2.29999995231628</v>
+        <v>2.35999989509583</v>
       </c>
       <c r="E2132" t="n">
-        <v>2.29999995231628</v>
+        <v>2.35999989509583</v>
       </c>
       <c r="F2132" t="n">
-        <v>2.40000009536743</v>
+        <v>2.38000011444092</v>
       </c>
       <c r="G2132" t="s">
         <v>7</v>
@@ -49410,22 +49410,22 @@
     </row>
     <row r="2133">
       <c r="A2133" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2133" t="n">
-        <v>1875</v>
+        <v>6875</v>
       </c>
       <c r="C2133" t="n">
-        <v>2.48000001907349</v>
+        <v>2.40000009536743</v>
       </c>
       <c r="D2133" t="n">
-        <v>2.3199999332428</v>
+        <v>2.29999995231628</v>
       </c>
       <c r="E2133" t="n">
-        <v>2.3199999332428</v>
+        <v>2.29999995231628</v>
       </c>
       <c r="F2133" t="n">
-        <v>2.48000001907349</v>
+        <v>2.40000009536743</v>
       </c>
       <c r="G2133" t="s">
         <v>7</v>
@@ -49433,22 +49433,22 @@
     </row>
     <row r="2134">
       <c r="A2134" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2134" t="n">
-        <v>5000</v>
+        <v>1875</v>
       </c>
       <c r="C2134" t="n">
         <v>2.48000001907349</v>
       </c>
       <c r="D2134" t="n">
-        <v>2.40000009536743</v>
+        <v>2.3199999332428</v>
       </c>
       <c r="E2134" t="n">
-        <v>2.40000009536743</v>
+        <v>2.3199999332428</v>
       </c>
       <c r="F2134" t="n">
-        <v>2.40000009536743</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="G2134" t="s">
         <v>7</v>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49454,6 +49454,75 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2135">
+      <c r="A2135" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2135" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C2135" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2135" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2135" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2135" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2136" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2136" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2136" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2136" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B2137" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C2137" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2137" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2137" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2137" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2137" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49523,6 +49523,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2138">
+      <c r="A2138" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2138" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2138" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2138" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2138" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2138" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2138" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2139" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C2139" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2139" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2139" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2139" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2139" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49569,6 +49569,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2140">
+      <c r="A2140" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2140" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2140" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2140" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2140" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2140" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2140" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2141" t="n">
+        <v>625</v>
+      </c>
+      <c r="C2141" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2141" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2141" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2141" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="G2141" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49600,13 +49600,13 @@
         <v>625</v>
       </c>
       <c r="C2141" t="n">
-        <v>2.40000009536743</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="D2141" t="n">
-        <v>2.40000009536743</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="E2141" t="n">
-        <v>2.40000009536743</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="F2141" t="n">
         <v>2.48000001907349</v>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49615,6 +49615,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2142">
+      <c r="A2142" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2142" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2142" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D2142" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="E2142" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="F2142" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="G2142" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49638,6 +49638,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2143">
+      <c r="A2143" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2143" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2143" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D2143" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="E2143" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="F2143" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="G2143" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2144" t="n">
+        <v>3750</v>
+      </c>
+      <c r="C2144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2144" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49684,6 +49684,27 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2145">
+      <c r="A2145" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2145" t="n">
+        <v>3750</v>
+      </c>
+      <c r="C2145" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2145" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2145" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2145"/>
+      <c r="G2145" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49700,7 +49700,9 @@
       <c r="E2145" t="n">
         <v>2.5</v>
       </c>
-      <c r="F2145"/>
+      <c r="F2145" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G2145" t="s">
         <v>7</v>
       </c>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49707,6 +49707,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2146">
+      <c r="A2146" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B2146" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2146" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49730,6 +49730,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2147">
+      <c r="A2147" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2147" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2147" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2147" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49753,6 +49753,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2148">
+      <c r="A2148" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2148" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2148" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2148" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2148" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2148" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2148" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2149" t="n">
+        <v>625</v>
+      </c>
+      <c r="C2149" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2149" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2149" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2149"/>
+      <c r="G2149" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49792,8 +49792,31 @@
       <c r="E2149" t="n">
         <v>2.40000009536743</v>
       </c>
-      <c r="F2149"/>
+      <c r="F2149" t="n">
+        <v>2.40000009536743</v>
+      </c>
       <c r="G2149" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2150" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C2150" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2150" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2150" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2150"/>
+      <c r="G2150" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49815,7 +49815,9 @@
       <c r="E2150" t="n">
         <v>2.40000009536743</v>
       </c>
-      <c r="F2150"/>
+      <c r="F2150" t="n">
+        <v>2.40000009536743</v>
+      </c>
       <c r="G2150" t="s">
         <v>7</v>
       </c>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49822,6 +49822,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2151">
+      <c r="A2151" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2151" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2151" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2151" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2151" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2151" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2151" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49845,6 +49845,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2152">
+      <c r="A2152" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2152" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C2152" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2152" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2152" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2152" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2152" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49868,6 +49868,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2153">
+      <c r="A2153" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2153" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2153" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2153" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2153" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2153" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2153" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49891,6 +49891,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2154">
+      <c r="A2154" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2154" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2154" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2154" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2154" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2154" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2154" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -49914,6 +49914,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2155">
+      <c r="A2155" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2155" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2155" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2155" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2155" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2155" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2155" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2156" t="n">
+        <v>3750</v>
+      </c>
+      <c r="C2156" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D2156" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E2156" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F2156" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G2156" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -62902,6 +62902,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2157">
+      <c r="A2157" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2157" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2157" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2157" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E2157" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F2157" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G2157" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="H2157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2157" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -62931,6 +62931,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2158">
+      <c r="A2158" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2158" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2158" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2158" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E2158" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F2158" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="G2158" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="H2158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2158" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2159" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2159" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2159" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="E2159" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="F2159" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="G2159" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="H2159" t="n">
+        <v>3750</v>
+      </c>
+      <c r="I2159" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -62989,6 +62989,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2160">
+      <c r="A2160" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2160" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2160" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="D2160" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="E2160" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="F2160" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="G2160" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="H2160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2160" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2161" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2161" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D2161" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E2161" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F2161" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G2161" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="H2161" t="n">
+        <v>625</v>
+      </c>
+      <c r="I2161" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -63047,6 +63047,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2162">
+      <c r="A2162" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2162" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2162" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D2162" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E2162" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F2162" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G2162" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="H2162" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I2162" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -63076,6 +63076,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2163">
+      <c r="A2163" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2163" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2163" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D2163" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E2163" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F2163" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G2163" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="H2163" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I2163" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -63105,6 +63105,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2164">
+      <c r="A2164" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2164" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2164" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D2164" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E2164" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F2164" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G2164" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="H2164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2164" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GEL.MI.xlsx
+++ b/data/GEL.MI.xlsx
@@ -63134,6 +63134,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2165">
+      <c r="A2165" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2165" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2165" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D2165" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="E2165" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="F2165" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="G2165" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="H2165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2165" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2166" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2166" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="D2166" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E2166" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="F2166" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="G2166" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="H2166" t="n">
+        <v>1875</v>
+      </c>
+      <c r="I2166" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
